--- a/experiments/results/resnet_imagenet34/ImageNet-1K/DICE/adaptive/std/results.xlsx
+++ b/experiments/results/resnet_imagenet34/ImageNet-1K/DICE/adaptive/std/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -799,6 +799,80 @@
       <c r="K12" s="4" t="inlineStr">
         <is>
           <t>dice_p=65,ash_p=None,react_th=None,scale_th=0.35,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>94.18000000000001</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=65,ash_p=None,react_th=None,scale_th=0.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>95.48</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>29.42</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=65,ash_p=None,react_th=None,scale_th=1.0,type=std</t>
         </is>
       </c>
     </row>
